--- a/GroceryApplication/src/test/resources/groceryapp.xlsx
+++ b/GroceryApplication/src/test/resources/groceryapp.xlsx
@@ -5,17 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\eclipse-workspace\GroceryApplication\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Groceryapp\GroceryApplication\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C28ABA5-00A4-44C8-8B2C-27D083454CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458A8B43-0048-435B-9878-6DAAB3990F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{898BB86E-1442-4EEB-8EA4-2B57C31BBEB8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="4" xr2:uid="{898BB86E-1442-4EEB-8EA4-2B57C31BBEB8}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
     <sheet name="ManagenewsPage" sheetId="2" r:id="rId2"/>
     <sheet name="AdminusersPage" sheetId="3" r:id="rId3"/>
+    <sheet name="ManagecontactPage" sheetId="4" r:id="rId4"/>
+    <sheet name="ManagefootertextPage" sheetId="5" r:id="rId5"/>
+    <sheet name="ManagecategoryPage" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>Username</t>
   </si>
@@ -71,16 +75,33 @@
   </si>
   <si>
     <t>JKRowling</t>
+  </si>
+  <si>
+    <t>calicut</t>
+  </si>
+  <si>
+    <t>anu@ybl.com</t>
+  </si>
+  <si>
+    <t>75% off on juices</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -103,13 +124,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -545,4 +569,69 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85C31C8D-730D-4F38-892C-5FCB8F2122F7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B5FD43-E38C-48FF-9E00-5BD503E5BE88}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>9123456789</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{A3B0B906-D002-4AE5-B02C-15B8710D2228}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F91A45E0-9871-418A-BA9A-7B15B8AE6EBA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52328DD-AC0A-4995-BCF8-3F1C9119DFF9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>